--- a/new-stats/fc-kudrivka.xlsx
+++ b/new-stats/fc-kudrivka.xlsx
@@ -889,22 +889,58 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LNZ Cherkasy</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kudrivka</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>

--- a/new-stats/fc-kudrivka.xlsx
+++ b/new-stats/fc-kudrivka.xlsx
@@ -943,22 +943,58 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kudrivka</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bukovyna</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/new-stats/fc-kudrivka.xlsx
+++ b/new-stats/fc-kudrivka.xlsx
@@ -997,22 +997,58 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dyn. Kyiv</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kudrivka</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
